--- a/Config.xlsx
+++ b/Config.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8AEDFE-4CED-4E8C-9CBD-96C93F55DC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB227D1-49F3-4D70-916B-FA082F255FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="1755" windowWidth="18000" windowHeight="10200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>KEY</t>
   </si>
@@ -70,26 +70,25 @@
     <t>STATEMENT_DATE</t>
   </si>
   <si>
-    <t>27 OCT 2022</t>
-  </si>
-  <si>
-    <t>NOSTRO RECO 26TH OCT 2022.xlsx</t>
-  </si>
-  <si>
-    <t>C:\Users\RPA\Desktop\TestFolder\</t>
-  </si>
-  <si>
-    <t>Nostro Reco Report 27th Oct 2022_.xlsx</t>
+    <t>\\10.222.140.144\d\d\MIS\GLS\RPA_BOT\</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -112,14 +111,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -437,9 +439,6 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" t="s">
         <v>3</v>
       </c>
@@ -448,9 +447,6 @@
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
@@ -467,8 +463,8 @@
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -478,12 +474,13 @@
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="B8" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{6A4F96ED-FF18-43C0-AD29-F7F07FBF2315}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>